--- a/.claude/skills/testcase-generator/outputs/excel_exports/business_site/role_manage_import_export_testcases.xlsx
+++ b/.claude/skills/testcase-generator/outputs/excel_exports/business_site/role_manage_import_export_testcases.xlsx
@@ -244,7 +244,7 @@
       </c>
       <c r="L2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M2" t="inlineStr" s="2">
@@ -271,17 +271,17 @@
     <row r="3" ht="64" customHeight="1">
       <c r="A3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入成功</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D3" t="inlineStr" s="2">
@@ -333,7 +333,7 @@
       </c>
       <c r="L3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M3" t="inlineStr" s="2">
@@ -360,17 +360,17 @@
     <row r="4" ht="64" customHeight="1">
       <c r="A4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入成功</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D4" t="inlineStr" s="2">
@@ -447,17 +447,17 @@
     <row r="5" ht="64" customHeight="1">
       <c r="A5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入成功</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D5" t="inlineStr" s="2">
@@ -535,17 +535,17 @@
     <row r="6" ht="64" customHeight="1">
       <c r="A6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入成功</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D6" t="inlineStr" s="2">
@@ -621,17 +621,17 @@
     <row r="7" ht="64" customHeight="1">
       <c r="A7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入成功</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D7" t="inlineStr" s="2">
@@ -707,12 +707,12 @@
     <row r="8" ht="64" customHeight="1">
       <c r="A8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
@@ -795,17 +795,17 @@
     <row r="9" ht="64" customHeight="1">
       <c r="A9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">权限生效</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D9" t="inlineStr" s="2">
@@ -883,7 +883,7 @@
     <row r="10" ht="64" customHeight="1">
       <c r="A10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -968,17 +968,17 @@
     <row r="11" ht="64" customHeight="1">
       <c r="A11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入失败校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色名称</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D11" t="inlineStr" s="2">
@@ -1053,12 +1053,12 @@
     <row r="12" ht="64" customHeight="1">
       <c r="A12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入失败校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
@@ -1139,17 +1139,17 @@
     <row r="13" ht="64" customHeight="1">
       <c r="A13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入失败校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色编号</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D13" t="inlineStr" s="2">
@@ -1224,17 +1224,17 @@
     <row r="14" ht="64" customHeight="1">
       <c r="A14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入失败校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色编号</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D14" t="inlineStr" s="2">
@@ -1309,17 +1309,17 @@
     <row r="15" ht="64" customHeight="1">
       <c r="A15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入失败校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色编号</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D15" t="inlineStr" s="2">
@@ -1394,12 +1394,12 @@
     <row r="16" ht="64" customHeight="1">
       <c r="A16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入失败校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
@@ -1479,12 +1479,12 @@
     <row r="17" ht="64" customHeight="1">
       <c r="A17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入失败校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
@@ -1565,17 +1565,17 @@
     <row r="18" ht="64" customHeight="1">
       <c r="A18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入失败校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">模板表头</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D18" t="inlineStr" s="2">
@@ -1650,12 +1650,12 @@
     <row r="19" ht="64" customHeight="1">
       <c r="A19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入失败校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
@@ -1736,17 +1736,17 @@
     <row r="20" ht="64" customHeight="1">
       <c r="A20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入失败校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">文件内容</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="2">
@@ -1821,17 +1821,17 @@
     <row r="21" ht="64" customHeight="1">
       <c r="A21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入失败校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">文件内容</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="2">
@@ -1906,12 +1906,12 @@
     <row r="22" ht="64" customHeight="1">
       <c r="A22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入失败校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
@@ -1991,12 +1991,12 @@
     <row r="23" ht="64" customHeight="1">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入失败校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
@@ -2076,17 +2076,17 @@
     <row r="24" ht="64" customHeight="1">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入失败校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">文件解析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="2">
@@ -2162,12 +2162,12 @@
     <row r="25" ht="64" customHeight="1">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入失败校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
@@ -2247,12 +2247,12 @@
     <row r="26" ht="64" customHeight="1">
       <c r="A26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入失败校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
@@ -2332,17 +2332,17 @@
     <row r="27" ht="64" customHeight="1">
       <c r="A27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入失败校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">菜单权限</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="2">
@@ -2417,17 +2417,17 @@
     <row r="28" ht="64" customHeight="1">
       <c r="A28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入失败校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">菜单权限</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="2">
@@ -2503,12 +2503,12 @@
     <row r="29" ht="64" customHeight="1">
       <c r="A29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入失败校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
@@ -2588,17 +2588,17 @@
     <row r="30" ht="64" customHeight="1">
       <c r="A30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入失败校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">按钮权限</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D30" t="inlineStr" s="2">
@@ -2673,12 +2673,12 @@
     <row r="31" ht="64" customHeight="1">
       <c r="A31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入失败校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
@@ -2758,17 +2758,17 @@
     <row r="32" ht="64" customHeight="1">
       <c r="A32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入失败校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分配用户</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="2">
@@ -2844,12 +2844,12 @@
     <row r="33" ht="64" customHeight="1">
       <c r="A33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入失败校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
@@ -2929,12 +2929,12 @@
     <row r="34" ht="64" customHeight="1">
       <c r="A34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入失败校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
@@ -3014,17 +3014,17 @@
     <row r="35" ht="64" customHeight="1">
       <c r="A35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入失败校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据权限</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D35" t="inlineStr" s="2">
@@ -3099,17 +3099,17 @@
     <row r="36" ht="64" customHeight="1">
       <c r="A36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入失败校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据权限</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D36" t="inlineStr" s="2">
@@ -3185,12 +3185,12 @@
     <row r="37" ht="64" customHeight="1">
       <c r="A37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入失败校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
@@ -3271,7 +3271,7 @@
     <row r="38" ht="64" customHeight="1">
       <c r="A38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -3360,7 +3360,7 @@
     <row r="39" ht="64" customHeight="1">
       <c r="A39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -3444,12 +3444,12 @@
     <row r="40" ht="64" customHeight="1">
       <c r="A40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">权限控制</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M40" t="inlineStr" s="2">
@@ -3529,12 +3529,12 @@
     <row r="41" ht="64" customHeight="1">
       <c r="A41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">权限控制</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
@@ -3616,12 +3616,12 @@
     <row r="42" ht="64" customHeight="1">
       <c r="A42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">权限控制</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
@@ -3704,7 +3704,7 @@
     <row r="43" ht="64" customHeight="1">
       <c r="A43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -3791,12 +3791,12 @@
     <row r="44" ht="64" customHeight="1">
       <c r="A44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">审计追踪</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
@@ -3878,7 +3878,7 @@
     <row r="45" ht="64" customHeight="1">
       <c r="A45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -3966,7 +3966,7 @@
     <row r="46" ht="64" customHeight="1">
       <c r="A46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -4053,17 +4053,17 @@
     <row r="47" ht="64" customHeight="1">
       <c r="A47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">模板下载</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D47" t="inlineStr" s="2">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="L47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M47" t="inlineStr" s="2">
@@ -4141,17 +4141,17 @@
     <row r="48" ht="64" customHeight="1">
       <c r="A48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">模板下载</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D48" t="inlineStr" s="2">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="L48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M48" t="inlineStr" s="2">
@@ -4227,17 +4227,17 @@
     <row r="49" ht="64" customHeight="1">
       <c r="A49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">模板下载</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D49" t="inlineStr" s="2">
@@ -4315,17 +4315,17 @@
     <row r="50" ht="64" customHeight="1">
       <c r="A50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">模板下载</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D50" t="inlineStr" s="2">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="L50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M50" t="inlineStr" s="2">
@@ -4403,17 +4403,17 @@
     <row r="51" ht="64" customHeight="1">
       <c r="A51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">模板下载</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D51" t="inlineStr" s="2">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="L51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M51" t="inlineStr" s="2">
@@ -4491,12 +4491,12 @@
     <row r="52" ht="64" customHeight="1">
       <c r="A52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
@@ -4575,12 +4575,12 @@
     <row r="53" ht="64" customHeight="1">
       <c r="A53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
@@ -4662,7 +4662,7 @@
     <row r="54" ht="64" customHeight="1">
       <c r="A54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="L54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M54" t="inlineStr" s="2">
@@ -4748,12 +4748,12 @@
     <row r="55" ht="64" customHeight="1">
       <c r="A55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
@@ -4834,17 +4834,17 @@
     <row r="56" ht="64" customHeight="1">
       <c r="A56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出格式</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D56" t="inlineStr" s="2">
@@ -4920,12 +4920,12 @@
     <row r="57" ht="64" customHeight="1">
       <c r="A57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="L57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M57" t="inlineStr" s="2">
@@ -5007,17 +5007,17 @@
     <row r="58" ht="64" customHeight="1">
       <c r="A58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色管理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出异常</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D58" t="inlineStr" s="2">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="L58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M58" t="inlineStr" s="2">

--- a/.claude/skills/testcase-generator/outputs/excel_exports/business_site/role_manage_import_export_testcases.xlsx
+++ b/.claude/skills/testcase-generator/outputs/excel_exports/business_site/role_manage_import_export_testcases.xlsx
@@ -244,7 +244,7 @@
       </c>
       <c r="L2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M2" t="inlineStr" s="2">
@@ -333,7 +333,7 @@
       </c>
       <c r="L3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M3" t="inlineStr" s="2">
@@ -768,7 +768,7 @@
       </c>
       <c r="L8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M8" t="inlineStr" s="2">

--- a/.claude/skills/testcase-generator/outputs/excel_exports/business_site/role_manage_import_export_testcases.xlsx
+++ b/.claude/skills/testcase-generator/outputs/excel_exports/business_site/role_manage_import_export_testcases.xlsx
@@ -77,7 +77,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P58"/>
+  <dimension ref="A1:P42"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -182,27 +182,27 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">配置管理</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">角色管理</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">导入</t>
-        </is>
-      </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入成功</t>
+          <t xml:space="preserve">导入模板</t>
         </is>
       </c>
       <c r="D2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">仅填必填字段，导入成功</t>
+          <t xml:space="preserve">下载角色导入模板成功</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr" s="2">
@@ -217,24 +217,21 @@
       </c>
       <c r="H2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
-2. 已准备符合角色管理模板的 Excel 文件，包含 1 条角色数据，仅填写必填字段：角色名称、角色编号、状态、菜单权限、数据权限类型，且格式符合要求</t>
+          <t xml:space="preserve">普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限</t>
         </is>
       </c>
       <c r="I2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入配置管理 - 角色管理列表页
-2. 点击导入按钮打开导入弹窗
-3. 上传仅填写必填字段的角色 Excel 文件
-4. 查看导入提示、角色列表和角色配置详情</t>
+          <t xml:space="preserve">1. 进入配置管理下的角色管理列表页
+2. 点击列表上方的导入按钮
+3. 在导入弹窗中点击下载模版</t>
         </is>
       </c>
       <c r="J2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统提示 1 条数据导入成功
-2. 导入弹窗关闭，角色列表自动刷新
-3. 新导入角色的角色名称、角色编号、状态、菜单权限、数据权限类型与 Excel 内容一致，按钮权限为空
-4. 分配用户为空，数据权限按全部权限保存</t>
+          <t xml:space="preserve">1. 浏览器下载 Excel 模版文件
+2. 模版名称为角色管理模板
+3. 导入弹窗保持可操作，可继续上传 Excel 文件</t>
         </is>
       </c>
       <c r="K2" t="inlineStr" s="2">
@@ -286,12 +283,12 @@
       </c>
       <c r="D3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">填写全部字段，导入成功</t>
+          <t xml:space="preserve">模板表头和批注显示正确</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr" s="2">
@@ -301,29 +298,25 @@
       </c>
       <c r="G3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">正例</t>
+          <t xml:space="preserve">UI</t>
         </is>
       </c>
       <c r="H3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
-2. 已准备符合角色管理模板的 Excel 文件，包含 3 条完整填写全部字段的角色数据：角色名称、角色编号、状态、菜单权限、按钮权限、分配用户、数据权限类型、数据权限，且格式符合要求</t>
+          <t xml:space="preserve">普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限</t>
         </is>
       </c>
       <c r="I3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入配置管理 - 角色管理列表页
-2. 点击导入按钮打开导入弹窗
-3. 上传全部字段均填写的角色 Excel 文件
-4. 查看导入结果和角色详情</t>
+          <t xml:space="preserve">1. 下载角色管理导入模版
+2. 打开 Excel 模版并查看表头、下拉选项和悬停批注</t>
         </is>
       </c>
       <c r="J3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统提示 3 条数据导入成功
-2. 导入弹窗关闭，角色列表自动刷新
-3. 新导入角色的角色名称、角色编号、状态、菜单权限、按钮权限、分配用户、数据权限类型、数据权限与 Excel 内容一致
-4. 分配用户关系和数据权限配置同时写入，并可在角色详情中查看</t>
+          <t xml:space="preserve">1. 模版包含角色名称、角色编码、状态、菜单权限、按钮权限、分配用户、数据权限类型、数据权限表头
+2. 状态下拉选项包含正常、停用；数据权限类型下拉选项包含全部权限、指定权限
+3. 表头批注展示必填性、长度、格式和多值分隔说明</t>
         </is>
       </c>
       <c r="K3" t="inlineStr" s="2">
@@ -333,7 +326,7 @@
       </c>
       <c r="L3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M3" t="inlineStr" s="2">
@@ -370,12 +363,12 @@
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">导入成功</t>
         </is>
       </c>
       <c r="D4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">全部权限下数据权限任意填写，导入成功</t>
+          <t xml:space="preserve">只填必填字段导入成功</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -395,22 +388,23 @@
       </c>
       <c r="H4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已准备符合角色管理模板的 Excel 文件，数据权限类型为全部权限，数据权限填写全部、留空、产品名称(产品编号)或其他任意内容，其他字段均符合导入规则</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 系统不存在角色编码 RM_IMPORT_001
+3. 待上传 Excel 为 .xlsx 格式，填写角色名称、角色编码、状态、菜单权限、按钮权限和数据权限类型，分配用户和数据权限为空</t>
         </is>
       </c>
       <c r="I4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并上传该 Excel 文件
-2. 打开导入角色的配置详情查看数据权限</t>
+          <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
+2. 上传待上传 Excel 文件
+3. 查看导入结果和角色列表</t>
         </is>
       </c>
       <c r="J4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 角色导入成功
-2. 数据权限类型按全部权限保存
-3. 角色列表中该角色的数据权限展示为全部且可点击查看详情
-4. 数据权限字段填写的任意内容不影响导入结果，导入后均按全部权限生效</t>
+          <t xml:space="preserve">1. 页面提示 1 条数据导入成功
+2. 导入弹窗关闭，角色列表新增 RM_IMPORT_001 对应角色
+3. 新增角色的状态、菜单权限和按钮权限与 Excel 内容一致</t>
         </is>
       </c>
       <c r="K4" t="inlineStr" s="2">
@@ -462,7 +456,7 @@
       </c>
       <c r="D5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">选择指定权限产品，导入成功</t>
+          <t xml:space="preserve">指定权限和用户导入成功</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -482,23 +476,24 @@
       </c>
       <c r="H5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 系统已存在产品：维生素A片(VIT-001)、阿托伐他汀钙片(TAB-005)
-3. 已准备符合角色管理模板的 Excel 文件，数据权限类型为指定权限，数据权限填写上述两个产品，且格式符合要求</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 系统已存在用户张三(zhangsan01)和产品维生素A片(VIT-001)
+3. 系统不存在角色编码 RM_IMPORT_002
+4. 待上传 Excel 中数据权限类型为指定权限，数据权限填写维生素A片(VIT-001)，分配用户填写张三(zhangsan01)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并上传该 Excel 文件
-2. 查看导入角色的数据权限详情</t>
+          <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
+2. 上传待上传 Excel 文件
+3. 查看角色详情、产品数据权限和分配用户详情</t>
         </is>
       </c>
       <c r="J5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 角色导入成功
-2. 数据权限类型保存为指定权限
-3. 数据权限详情展示维生素A片(VIT-001)和阿托伐他汀钙片(TAB-005)
-4. 角色列表中该角色的数据权限显示 2 个产品或等价统计值</t>
+          <t xml:space="preserve">1. 页面提示 1 条数据导入成功
+2. 角色列表新增 RM_IMPORT_002 对应角色
+3. 产品数据权限详情显示维生素A片和 VIT-001，分配用户详情显示张三和 zhangsan01</t>
         </is>
       </c>
       <c r="K5" t="inlineStr" s="2">
@@ -550,12 +545,12 @@
       </c>
       <c r="D6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色名称100字符，导入成功</t>
+          <t xml:space="preserve">多行角色整体导入成功</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr" s="2">
@@ -565,26 +560,28 @@
       </c>
       <c r="G6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">边界</t>
+          <t xml:space="preserve">正例</t>
         </is>
       </c>
       <c r="H6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已准备符合角色管理模板的 Excel 文件，角色名称填写 100 个字符，其他必填字段格式合法</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 系统不存在角色编码 RM_IMPORT_003、RM_IMPORT_004、RM_IMPORT_005
+3. 待上传 Excel 包含 3 行合法角色数据</t>
         </is>
       </c>
       <c r="I6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并上传该 Excel 文件
-2. 查看导入提示、角色列表和角色详情</t>
+          <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
+2. 上传包含 3 行合法数据的 Excel 文件
+3. 查看导入结果和角色列表</t>
         </is>
       </c>
       <c r="J6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 角色导入成功
-2. 角色详情中角色名称完整保存 100 个字符，无截断或自动变更
-3. 角色列表可按该角色名称查询到新导入角色</t>
+          <t xml:space="preserve">1. 页面提示 3 条数据导入成功
+2. 角色列表新增 3 条对应角色记录
+3. 每条角色的基础信息、状态、菜单权限、按钮权限、分配用户和数据权限与 Excel 内容一致</t>
         </is>
       </c>
       <c r="K6" t="inlineStr" s="2">
@@ -636,12 +633,12 @@
       </c>
       <c r="D7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色编号50字符，导入成功</t>
+          <t xml:space="preserve">导入后角色权限生效</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr" s="2">
@@ -651,36 +648,38 @@
       </c>
       <c r="G7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">边界</t>
+          <t xml:space="preserve">回归</t>
         </is>
       </c>
       <c r="H7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已准备符合角色管理模板的 Excel 文件，角色编号填写 50 个字符的大小写字母、数字或下划线组合，其他必填字段格式合法</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 系统已存在用户李四(lisi02)和产品阿托伐他汀钙片(TAB-005)
+3. 待上传 Excel 包含角色 RM_IMPORT_006，菜单权限包含计划管理/年度计划设置，按钮权限包含计划管理/年度计划设置:新增，分配用户为李四(lisi02)，数据权限为阿托伐他汀钙片(TAB-005)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并上传该 Excel 文件
-2. 查看导入提示、角色列表和角色详情</t>
+          <t xml:space="preserve">1. 导入角色 RM_IMPORT_006
+2. 使用李四账号重新登录业务站点 A
+3. 进入年度计划设置列表并点击新增</t>
         </is>
       </c>
       <c r="J7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 角色导入成功
-2. 角色详情中角色编号完整保存 50 个字符，无截断或自动变更
-3. 角色列表可按该角色编号查询到新导入角色</t>
+          <t xml:space="preserve">1. 李四可见年度计划设置菜单和新增按钮
+2. 新增计划弹窗的所属产品下拉仅展示阿托伐他汀钙片
+3. 不在该角色权限内的菜单或按钮不展示</t>
         </is>
       </c>
       <c r="K7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、user_roles.md</t>
         </is>
       </c>
       <c r="L7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M7" t="inlineStr" s="2">
@@ -717,17 +716,17 @@
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">权限生效</t>
+          <t xml:space="preserve">导入失败校验</t>
         </is>
       </c>
       <c r="D8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入菜单按钮权限后，权限生效</t>
+          <t xml:space="preserve">非 Excel 文件上传失败</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr" s="2">
@@ -737,38 +736,36 @@
       </c>
       <c r="G8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">联动</t>
+          <t xml:space="preserve">反例</t>
         </is>
       </c>
       <c r="H8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A，拥有角色管理导入按钮权限
-2. Excel 文件中角色 R 配置年度计划设置菜单及新增按钮权限，分配给用户 U，数据权限类型为全部权限，且格式符合要求
-3. 用户 U 当前无年度计划设置菜单和新增按钮权限</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 待上传文件为 .txt 格式</t>
         </is>
       </c>
       <c r="I8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 在角色管理列表页导入该 Excel 文件
-2. 用户 U 重新登录业务站点 A
-3. 进入年度计划设置并点击新增按钮</t>
+          <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
+2. 上传 .txt 文件</t>
         </is>
       </c>
       <c r="J8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 用户 U 重新登录后可见年度计划设置菜单和新增按钮
-2. 新增入口可正常打开
-3. 导入角色的菜单权限、按钮权限和分配用户关系同时生效</t>
+          <t xml:space="preserve">1. 系统阻止上传或导入
+2. 页面提示请上传 Excel 文件（.xlsx或.xls格式）
+3. 角色列表不新增数据</t>
         </is>
       </c>
       <c r="K8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、user_roles.md</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M8" t="inlineStr" s="2">
@@ -810,12 +807,12 @@
       </c>
       <c r="D9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入产品权限后，过滤生效</t>
+          <t xml:space="preserve">文件超过20MB上传失败</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="F9" t="inlineStr" s="2">
@@ -825,33 +822,31 @@
       </c>
       <c r="G9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">联动</t>
+          <t xml:space="preserve">边界</t>
         </is>
       </c>
       <c r="H9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A，拥有角色管理导入按钮权限
-2. Excel 文件中角色 R 分配给用户 U，数据权限类型为指定权限，数据权限填写产品 P1，且格式符合要求
-3. 年度计划设置、任务管理和报告编制中同时存在产品 P1 与 P2 的业务数据</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 待上传 Excel 文件大小超过 20MB</t>
         </is>
       </c>
       <c r="I9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 在角色管理列表页导入该 Excel 文件
-2. 用户 U 重新登录业务站点 A
-3. 分别进入年度计划设置、任务管理和报告编制查看数据范围</t>
+          <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
+2. 上传超过 20MB 的 Excel 文件</t>
         </is>
       </c>
       <c r="J9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 用户 U 仅能查看产品 P1 权限范围内的数据
-2. 所属产品下拉框只展示产品 P1
-3. 产品 P2 数据不可见且不能被直接引用</t>
+          <t xml:space="preserve">1. 系统阻止上传或导入
+2. 页面提示文件大小不可超过20M
+3. 角色列表不新增数据</t>
         </is>
       </c>
       <c r="K9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、user_roles.md</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L9" t="inlineStr" s="2">
@@ -888,17 +883,17 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入失败校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色名称</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色名称为空，导入失败</t>
+          <t xml:space="preserve">空文件导入失败</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
@@ -918,20 +913,21 @@
       </c>
       <c r="H10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已准备符合模板的 Excel 文件，其中角色名称为空，其他字段均符合导入规则</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 待上传 Excel 文件为空文件</t>
         </is>
       </c>
       <c r="I10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并上传该 Excel 文件
-2. 下载TXT错误报告并核对角色列表</t>
+          <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
+2. 上传空 Excel 文件</t>
         </is>
       </c>
       <c r="J10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统拒绝全部导入，不新增角色数据
-2. TXT错误报告包含错误行号和角色名称必填原因</t>
+          <t xml:space="preserve">1. 系统终止导入
+2. 页面提示文件为空，暂不支持导入
+3. 角色列表不新增数据</t>
         </is>
       </c>
       <c r="K10" t="inlineStr" s="2">
@@ -983,7 +979,7 @@
       </c>
       <c r="D11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色名称超过100字符，导入失败</t>
+          <t xml:space="preserve">有表头无数据导入失败</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
@@ -998,30 +994,31 @@
       </c>
       <c r="G11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">边界</t>
+          <t xml:space="preserve">反例</t>
         </is>
       </c>
       <c r="H11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已准备符合模板的 Excel 文件，其中角色名称填写 101 个字符，其他字段均符合导入规则</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 待上传 Excel 文件表头正确但无有效数据行</t>
         </is>
       </c>
       <c r="I11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并上传该 Excel 文件
-2. 下载TXT错误报告并核对角色列表</t>
+          <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
+2. 上传有表头无数据的 Excel 文件</t>
         </is>
       </c>
       <c r="J11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统拒绝全部导入，不新增角色数据
-2. TXT错误报告包含错误行号和角色名称最大长度100个字符的原因</t>
+          <t xml:space="preserve">1. 系统终止导入
+2. 页面提示文件中无有效数据，请检查后重新上传
+3. 角色列表不新增数据</t>
         </is>
       </c>
       <c r="K11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、boundary_value_template.md</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L11" t="inlineStr" s="2">
@@ -1063,12 +1060,12 @@
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色编号</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色编号重复，导入失败</t>
+          <t xml:space="preserve">有数据无表头导入失败</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
@@ -1088,26 +1085,26 @@
       </c>
       <c r="H12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A，拥有角色管理导入按钮权限
-2. 已准备 Excel 文件，其中 1 行角色编号重复，其他行均满足导入规则</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 待上传 Excel 文件存在数据行但表头为空或缺失</t>
         </is>
       </c>
       <c r="I12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页
-2. 上传该 Excel 文件执行导入
-3. 下载TXT错误报告并核对角色列表和用户关系</t>
+          <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
+2. 上传有数据无表头的 Excel 文件</t>
         </is>
       </c>
       <c r="J12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统拒绝整份文件导入
-2. TXT错误报告包含重复角色编号所在行号和原因</t>
+          <t xml:space="preserve">1. 系统终止导入
+2. 页面提示表头信息存在空值，暂不支持分析
+3. 角色列表不新增数据</t>
         </is>
       </c>
       <c r="K12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、negative_flow_template.md</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L12" t="inlineStr" s="2">
@@ -1154,7 +1151,7 @@
       </c>
       <c r="D13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色编号为空，导入失败</t>
+          <t xml:space="preserve">表头不匹配模板导入失败</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
@@ -1174,20 +1171,21 @@
       </c>
       <c r="H13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已准备符合模板的 Excel 文件，其中角色编号为空，其他字段均符合导入规则</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 待上传 Excel 文件表头与系统角色管理模版不一致</t>
         </is>
       </c>
       <c r="I13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并上传该 Excel 文件
-2. 下载TXT错误报告并核对角色列表</t>
+          <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
+2. 上传表头不匹配的 Excel 文件</t>
         </is>
       </c>
       <c r="J13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统拒绝全部导入，不新增角色数据
-2. TXT错误报告包含错误行号和角色编号必填原因</t>
+          <t xml:space="preserve">1. 系统终止导入
+2. 页面提示导入文件的表头与系统模版不一致，请重新下载模版后填写
+3. 角色列表不新增数据</t>
         </is>
       </c>
       <c r="K13" t="inlineStr" s="2">
@@ -1239,7 +1237,7 @@
       </c>
       <c r="D14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色编号格式不正确，导入失败</t>
+          <t xml:space="preserve">合并单元格导入失败</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
@@ -1259,20 +1257,21 @@
       </c>
       <c r="H14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已准备符合模板的 Excel 文件，其中角色编号包含空格或特殊字符，其他字段均符合导入规则</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 待上传 Excel 文件中存在合并单元格</t>
         </is>
       </c>
       <c r="I14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并上传该 Excel 文件
-2. 下载TXT错误报告并核对角色列表</t>
+          <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
+2. 上传包含合并单元格的 Excel 文件</t>
         </is>
       </c>
       <c r="J14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统拒绝全部导入，不新增角色数据
-2. TXT错误报告包含错误行号和角色编号仅支持大小写字母、数字、下划线的原因</t>
+          <t xml:space="preserve">1. 系统终止导入
+2. 页面提示文件中存在合并单元格，暂不支持。请处理后重新上传。
+3. 角色列表不新增数据</t>
         </is>
       </c>
       <c r="K14" t="inlineStr" s="2">
@@ -1324,7 +1323,7 @@
       </c>
       <c r="D15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">角色编号超过50字符，导入失败</t>
+          <t xml:space="preserve">加密文件解析失败</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
@@ -1339,30 +1338,31 @@
       </c>
       <c r="G15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">边界</t>
+          <t xml:space="preserve">反例</t>
         </is>
       </c>
       <c r="H15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已准备符合模板的 Excel 文件，其中角色编号填写 51 个字符，其他字段均符合导入规则</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 待上传 Excel 文件已加密或被加密软件处理导致无法解析</t>
         </is>
       </c>
       <c r="I15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并上传该 Excel 文件
-2. 下载TXT错误报告并核对角色列表</t>
+          <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
+2. 上传加密 Excel 文件</t>
         </is>
       </c>
       <c r="J15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统拒绝全部导入，不新增角色数据
-2. TXT错误报告包含错误行号和角色编号最大长度50个字符的原因</t>
+          <t xml:space="preserve">1. 系统终止导入
+2. 页面提示 Excel解析失败，请检查格式等信息。
+3. 角色列表不新增数据</t>
         </is>
       </c>
       <c r="K15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、boundary_value_template.md</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L15" t="inlineStr" s="2">
@@ -1404,12 +1404,12 @@
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">文件格式</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">非Excel文件，上传失败</t>
+          <t xml:space="preserve">文件损坏或已删除导入失败</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
@@ -1429,20 +1429,21 @@
       </c>
       <c r="H16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已准备 .txt 或 .csv 文件</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 待上传 Excel 文件损坏或服务器临时文件已被删除</t>
         </is>
       </c>
       <c r="I16" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
-2. 上传非 Excel 文件</t>
+2. 上传损坏文件或触发上传后文件不存在场景</t>
         </is>
       </c>
       <c r="J16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统提示请上传Excel文件（.xlsx或.xls格式）
-2. 文件不进入有效导入流程</t>
+          <t xml:space="preserve">1. 系统终止导入
+2. 页面提示文件已不存在或格式错误，请检查文件。
+3. 角色列表不新增数据</t>
         </is>
       </c>
       <c r="K16" t="inlineStr" s="2">
@@ -1489,12 +1490,12 @@
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">模板表头</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">表头不匹配模板，导入失败</t>
+          <t xml:space="preserve">角色名称为空导入失败</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
@@ -1514,26 +1515,27 @@
       </c>
       <c r="H17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已准备 .xlsx 文件，表头缺少角色编号或菜单权限字段</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 待上传 Excel 中角色名称为空，其他必填字段合法</t>
         </is>
       </c>
       <c r="I17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并上传表头不匹配的 Excel 文件
-2. 查看导入结果</t>
+          <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
+2. 上传角色名称为空的 Excel 文件
+3. 下载并查看 TXT 错误报告</t>
         </is>
       </c>
       <c r="J17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统提示导入文件的表头与系统模版不一致，请重新下载模版后填写
-2. 导入流程终止，不写入任何角色数据
-3. 导入弹窗保持开启，用户可重新上传文件</t>
+          <t xml:space="preserve">1. 系统拒绝全部导入
+2. 错误报告记录对应行号和角色名称必填原因
+3. 角色列表不新增该行角色数据</t>
         </is>
       </c>
       <c r="K17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
         </is>
       </c>
       <c r="L17" t="inlineStr" s="2">
@@ -1580,7 +1582,7 @@
       </c>
       <c r="D18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">有数据无表头，导入失败</t>
+          <t xml:space="preserve">角色名称超长导入失败</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -1595,30 +1597,32 @@
       </c>
       <c r="G18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">反例</t>
+          <t xml:space="preserve">边界</t>
         </is>
       </c>
       <c r="H18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已准备存在角色数据但表头为空或表头信息缺失的 Excel 文件</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 待上传 Excel 中角色名称超过 100 个字符，其他字段合法</t>
         </is>
       </c>
       <c r="I18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并上传该 Excel 文件
-2. 查看页面提示和导入结果</t>
+          <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
+2. 上传角色名称超长的 Excel 文件
+3. 下载并查看 TXT 错误报告</t>
         </is>
       </c>
       <c r="J18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统提示表头信息存在空值，暂不支持分析
-2. 导入流程终止</t>
+          <t xml:space="preserve">1. 系统拒绝全部导入
+2. 错误报告记录对应行号和角色名称最大支持 100 个字符的失败原因
+3. 角色列表不新增该行角色数据</t>
         </is>
       </c>
       <c r="K18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
         </is>
       </c>
       <c r="L18" t="inlineStr" s="2">
@@ -1660,12 +1664,12 @@
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">文件内容</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">有表头无数据，导入失败</t>
+          <t xml:space="preserve">角色编码为空导入失败</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
@@ -1680,31 +1684,32 @@
       </c>
       <c r="G19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">边界</t>
+          <t xml:space="preserve">反例</t>
         </is>
       </c>
       <c r="H19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已准备仅包含模板表头但无角色数据行的 Excel 文件</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 待上传 Excel 中角色编码为空，其他必填字段合法</t>
         </is>
       </c>
       <c r="I19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并上传该 Excel 文件
-2. 查看页面提示和导入结果</t>
+          <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
+2. 上传角色编码为空的 Excel 文件
+3. 下载并查看 TXT 错误报告</t>
         </is>
       </c>
       <c r="J19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统提示文件中无有效数据，请检查后重新上传
-2. 不生成错误角色数据
-3. 导入弹窗保持开启便于重新上传</t>
+          <t xml:space="preserve">1. 系统拒绝全部导入
+2. 错误报告记录对应行号和角色编码必填原因
+3. 角色列表不新增该行角色数据</t>
         </is>
       </c>
       <c r="K19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、boundary_value_template.md</t>
+          <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
         </is>
       </c>
       <c r="L19" t="inlineStr" s="2">
@@ -1751,7 +1756,7 @@
       </c>
       <c r="D20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">空文件，导入失败</t>
+          <t xml:space="preserve">角色编码重复导入失败</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
@@ -1766,30 +1771,33 @@
       </c>
       <c r="G20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">边界</t>
+          <t xml:space="preserve">反例</t>
         </is>
       </c>
       <c r="H20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已准备大小为 0 或无任何工作表内容的 Excel 文件</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 系统已存在角色编码 RM_EXIST_001
+3. 待上传 Excel 中角色编码填写 RM_EXIST_001</t>
         </is>
       </c>
       <c r="I20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并上传空文件
-2. 查看页面提示和导入结果</t>
+          <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
+2. 上传角色编码重复的 Excel 文件
+3. 下载并查看 TXT 错误报告</t>
         </is>
       </c>
       <c r="J20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统提示文件为空，暂不支持导入
-2. 文件不进入逐行业务校验</t>
+          <t xml:space="preserve">1. 系统拒绝全部导入
+2. 错误报告记录对应行号和角色编码重复原因
+3. 原有 RM_EXIST_001 角色数据不被覆盖或修改</t>
         </is>
       </c>
       <c r="K20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、boundary_value_template.md</t>
+          <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
         </is>
       </c>
       <c r="L20" t="inlineStr" s="2">
@@ -1836,7 +1844,7 @@
       </c>
       <c r="D21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">合并单元格文件，导入失败</t>
+          <t xml:space="preserve">角色编码格式非法导入失败</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
@@ -1856,25 +1864,27 @@
       </c>
       <c r="H21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已准备包含合并单元格的角色 Excel 文件</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 待上传 Excel 中角色编码包含小写字母、中文或特殊字符</t>
         </is>
       </c>
       <c r="I21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并上传该 Excel 文件
-2. 查看页面提示和角色列表</t>
+          <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
+2. 上传角色编码格式非法的 Excel 文件
+3. 下载并查看 TXT 错误报告</t>
         </is>
       </c>
       <c r="J21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统提示文件中存在合并单元格，暂不支持，请处理后重新上传
-2. 导入流程终止</t>
+          <t xml:space="preserve">1. 系统拒绝全部导入
+2. 错误报告记录对应行号和角色编码仅支持大写字母、数字、下划线的失败原因
+3. 角色列表不新增该行角色数据</t>
         </is>
       </c>
       <c r="K21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、negative_flow_template.md</t>
+          <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
         </is>
       </c>
       <c r="L21" t="inlineStr" s="2">
@@ -1916,12 +1926,12 @@
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">文件大小</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">文件超过20M，导入失败</t>
+          <t xml:space="preserve">角色编码超长导入失败</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
@@ -1941,25 +1951,27 @@
       </c>
       <c r="H22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已准备大小超过 20MB 的 .xlsx 文件</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 待上传 Excel 中角色编码超过 50 个字符，其他字段合法</t>
         </is>
       </c>
       <c r="I22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并上传超过 20MB 的文件
-2. 查看页面提示和导入结果</t>
+          <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
+2. 上传角色编码超长的 Excel 文件
+3. 下载并查看 TXT 错误报告</t>
         </is>
       </c>
       <c r="J22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统提示文件大小不可超过20M
-2. 文件不进入导入校验和写入流程</t>
+          <t xml:space="preserve">1. 系统拒绝全部导入
+2. 错误报告记录对应行号和角色编码最大长度 50 个字符的失败原因
+3. 角色列表不新增该行角色数据</t>
         </is>
       </c>
       <c r="K22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、boundary_value_template.md</t>
+          <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
         </is>
       </c>
       <c r="L22" t="inlineStr" s="2">
@@ -2001,12 +2013,12 @@
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">文件解析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">加密文件解析失败，导入失败</t>
+          <t xml:space="preserve">状态值非法导入失败</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
@@ -2026,25 +2038,27 @@
       </c>
       <c r="H23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已准备被加密软件处理或受保护导致无法解析的 Excel 文件</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 待上传 Excel 中状态填写非正常、停用的值</t>
         </is>
       </c>
       <c r="I23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并上传该 Excel 文件
-2. 查看页面提示和导入结果</t>
+          <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
+2. 上传状态值非法的 Excel 文件
+3. 下载并查看 TXT 错误报告</t>
         </is>
       </c>
       <c r="J23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统提示Excel解析失败，请检查格式等信息
-2. 不执行逐行导入</t>
+          <t xml:space="preserve">1. 系统拒绝全部导入
+2. 错误报告记录对应行号和状态值不在允许选项内的失败原因
+3. 角色列表不新增该行角色数据</t>
         </is>
       </c>
       <c r="K23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、negative_flow_template.md</t>
+          <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
         </is>
       </c>
       <c r="L23" t="inlineStr" s="2">
@@ -2091,7 +2105,7 @@
       </c>
       <c r="D24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">文件损坏，导入失败</t>
+          <t xml:space="preserve">菜单权限路径无效导入失败</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
@@ -2111,26 +2125,27 @@
       </c>
       <c r="H24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已准备上传后被删除或格式损坏的 Excel 文件</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 待上传 Excel 中菜单权限包含系统不存在的菜单路径</t>
         </is>
       </c>
       <c r="I24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并上传该 Excel 文件
-2. 在系统读取文件时触发损坏或文件不存在状态
-3. 查看页面提示</t>
+          <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
+2. 上传菜单权限路径无效的 Excel 文件
+3. 下载并查看 TXT 错误报告</t>
         </is>
       </c>
       <c r="J24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统提示文件已不存在或格式错误，请检查文件
-2. 导入流程终止</t>
+          <t xml:space="preserve">1. 系统拒绝全部导入
+2. 错误报告记录对应行号和菜单路径无效原因
+3. 角色列表不新增该行角色数据</t>
         </is>
       </c>
       <c r="K24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、negative_flow_template.md</t>
+          <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
         </is>
       </c>
       <c r="L24" t="inlineStr" s="2">
@@ -2172,12 +2187,12 @@
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">状态</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">状态为空，导入失败</t>
+          <t xml:space="preserve">按钮权限格式非法导入失败</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
@@ -2197,25 +2212,27 @@
       </c>
       <c r="H25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已准备符合模板的 Excel 文件，其中状态为空，其他字段均符合导入规则</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 待上传 Excel 中按钮权限未按菜单路径:按钮名称格式填写</t>
         </is>
       </c>
       <c r="I25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并上传该 Excel 文件
-2. 下载TXT错误报告并核对角色列表</t>
+          <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
+2. 上传按钮权限格式非法的 Excel 文件
+3. 下载并查看 TXT 错误报告</t>
         </is>
       </c>
       <c r="J25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统拒绝全部导入，不新增角色数据
-2. TXT错误报告包含错误行号和状态必填原因</t>
+          <t xml:space="preserve">1. 系统拒绝全部导入
+2. 错误报告记录对应行号和按钮权限格式错误原因
+3. 角色列表不新增该行角色数据</t>
         </is>
       </c>
       <c r="K25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
         </is>
       </c>
       <c r="L25" t="inlineStr" s="2">
@@ -2257,12 +2274,12 @@
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">菜单权限</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">菜单权限为空，导入失败</t>
+          <t xml:space="preserve">按钮名称不存在导入失败</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
@@ -2282,25 +2299,27 @@
       </c>
       <c r="H26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已准备符合模板的 Excel 文件，其中菜单权限为空，其他字段均符合导入规则</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 待上传 Excel 中按钮权限包含系统内不存在的按钮名称</t>
         </is>
       </c>
       <c r="I26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并上传该 Excel 文件
-2. 下载TXT错误报告并核对角色列表</t>
+          <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
+2. 上传按钮名称不存在的 Excel 文件
+3. 下载并查看 TXT 错误报告</t>
         </is>
       </c>
       <c r="J26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统拒绝全部导入，不新增角色权限数据
-2. TXT错误报告包含错误行号和菜单权限必填原因</t>
+          <t xml:space="preserve">1. 系统拒绝全部导入
+2. 错误报告记录对应行号和按钮名称与系统按钮不一致的失败原因
+3. 角色列表不新增该行角色数据</t>
         </is>
       </c>
       <c r="K26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
         </is>
       </c>
       <c r="L26" t="inlineStr" s="2">
@@ -2347,7 +2366,7 @@
       </c>
       <c r="D27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">菜单权限格式不正确，导入失败</t>
+          <t xml:space="preserve">分配用户不存在导入失败</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
@@ -2367,25 +2386,27 @@
       </c>
       <c r="H27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已准备符合模板的 Excel 文件，其中菜单权限未按父菜单/子菜单层级路径填写或多个菜单未用顿号分隔，其他字段均符合导入规则</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 待上传 Excel 中分配用户填写系统不存在的姓名和用户账号</t>
         </is>
       </c>
       <c r="I27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并上传该 Excel 文件
-2. 下载TXT错误报告并核对角色列表</t>
+          <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
+2. 上传分配用户不存在的 Excel 文件
+3. 下载并查看 TXT 错误报告</t>
         </is>
       </c>
       <c r="J27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统拒绝全部导入，不新增角色权限数据
-2. TXT错误报告包含错误行号和菜单权限格式不正确原因</t>
+          <t xml:space="preserve">1. 系统拒绝全部导入
+2. 错误报告记录对应行号和用户账号不存在原因
+3. 角色列表不新增该行角色数据</t>
         </is>
       </c>
       <c r="K27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
         </is>
       </c>
       <c r="L27" t="inlineStr" s="2">
@@ -2432,7 +2453,7 @@
       </c>
       <c r="D28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">菜单路径无效，导入失败</t>
+          <t xml:space="preserve">数据权限类型为空导入失败</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
@@ -2452,26 +2473,27 @@
       </c>
       <c r="H28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已准备符合模板的 Excel 文件，其中菜单权限填写系统不存在的层级路径
-3. 文件中其余字段均符合导入规则</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 待上传 Excel 中数据权限类型为空，其他字段合法</t>
         </is>
       </c>
       <c r="I28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并上传该 Excel 文件
-2. 下载TXT错误报告并查看角色列表</t>
+          <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
+2. 上传数据权限类型为空的 Excel 文件
+3. 下载并查看 TXT 错误报告</t>
         </is>
       </c>
       <c r="J28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统拒绝全部导入，不新增角色权限数据
-2. TXT错误报告包含错误行号和菜单路径无效原因</t>
+          <t xml:space="preserve">1. 系统拒绝全部导入
+2. 错误报告记录对应行号和数据权限类型必填原因
+3. 角色列表不新增该行角色数据</t>
         </is>
       </c>
       <c r="K28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
         </is>
       </c>
       <c r="L28" t="inlineStr" s="2">
@@ -2513,12 +2535,12 @@
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">按钮权限</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">按钮权限格式无效，导入失败</t>
+          <t xml:space="preserve">指定权限未填产品导入失败</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
@@ -2538,25 +2560,27 @@
       </c>
       <c r="H29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已准备符合模板的 Excel 文件，其中按钮权限未按“菜单路径:按钮名称”填写，其他字段均符合导入规则</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 待上传 Excel 中数据权限类型为指定权限，数据权限为空</t>
         </is>
       </c>
       <c r="I29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并上传该 Excel 文件
-2. 下载并查看TXT错误报告</t>
+          <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
+2. 上传指定权限未填产品的 Excel 文件
+3. 下载并查看 TXT 错误报告</t>
         </is>
       </c>
       <c r="J29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统拒绝全部导入并提供TXT错误报告
-2. TXT错误报告包含错误行号和按钮权限格式无效原因</t>
+          <t xml:space="preserve">1. 系统拒绝全部导入
+2. 错误报告记录对应行号和指定权限时数据权限必填原因
+3. 角色列表不新增该行角色数据</t>
         </is>
       </c>
       <c r="K29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
         </is>
       </c>
       <c r="L29" t="inlineStr" s="2">
@@ -2603,7 +2627,7 @@
       </c>
       <c r="D30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">按钮名称不存在，导入失败</t>
+          <t xml:space="preserve">产品编号不存在导入失败</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
@@ -2623,25 +2647,27 @@
       </c>
       <c r="H30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已准备符合模板的 Excel 文件，其中按钮权限格式正确但按钮名称在对应菜单下不存在，其他字段均符合导入规则</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 待上传 Excel 中数据权限填写系统不存在的产品名称和产品编号</t>
         </is>
       </c>
       <c r="I30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并上传该 Excel 文件
-2. 下载并查看TXT错误报告</t>
+          <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
+2. 上传产品编号不存在的 Excel 文件
+3. 下载并查看 TXT 错误报告</t>
         </is>
       </c>
       <c r="J30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统拒绝全部导入并提供TXT错误报告
-2. TXT错误报告包含错误行号和按钮名称不存在原因</t>
+          <t xml:space="preserve">1. 系统拒绝全部导入
+2. 错误报告记录对应行号和产品编号不存在原因
+3. 角色列表不新增该行角色数据</t>
         </is>
       </c>
       <c r="K30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
         </is>
       </c>
       <c r="L30" t="inlineStr" s="2">
@@ -2683,12 +2709,12 @@
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分配用户</t>
+          <t xml:space="preserve">导入错误报告</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分配用户格式不正确，导入失败</t>
+          <t xml:space="preserve">多字段错误报告分号展示</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -2708,25 +2734,27 @@
       </c>
       <c r="H31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已准备符合模板的 Excel 文件，其中分配用户未按姓名(用户账号)格式填写，其他字段均符合导入规则</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 待上传 Excel 同一行同时存在角色编码重复、分配用户不存在、产品编号不存在错误</t>
         </is>
       </c>
       <c r="I31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并上传该 Excel 文件
-2. 下载TXT错误报告并核对角色列表和用户角色关系</t>
+          <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
+2. 上传包含多字段错误的 Excel 文件
+3. 下载并查看 TXT 错误报告</t>
         </is>
       </c>
       <c r="J31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统拒绝全部导入，不新增角色且不修改用户角色关系
-2. TXT错误报告包含错误行号和分配用户格式应为姓名(用户账号)的原因</t>
+          <t xml:space="preserve">1. 系统拒绝全部导入，导入弹窗保持开启
+2. TXT 错误报告按行号,错误原因格式展示
+3. 同一行多个错误原因使用分号分隔</t>
         </is>
       </c>
       <c r="K31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
         </is>
       </c>
       <c r="L31" t="inlineStr" s="2">
@@ -2773,12 +2801,12 @@
       </c>
       <c r="D32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分配用户不存在，导入失败</t>
+          <t xml:space="preserve">部分行错误整表回滚</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F32" t="inlineStr" s="2">
@@ -2788,31 +2816,32 @@
       </c>
       <c r="G32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">反例</t>
+          <t xml:space="preserve">回归</t>
         </is>
       </c>
       <c r="H32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已准备符合模板的 Excel 文件，其中分配用户填写不存在的姓名和用户账号
-3. 文件中其余字段均符合导入规则</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 待上传 Excel 包含 2 行合法角色和 1 行角色编码重复数据</t>
         </is>
       </c>
       <c r="I32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并上传该 Excel 文件
-2. 下载TXT错误报告并核对角色列表和用户角色关系</t>
+          <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
+2. 上传包含部分错误行的 Excel 文件
+3. 查看导入结果、错误报告和角色列表</t>
         </is>
       </c>
       <c r="J32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统拒绝全部导入，不新增角色且不修改用户角色关系
-2. TXT错误报告包含错误行号和用户账号不存在原因</t>
+          <t xml:space="preserve">1. 系统拒绝全部导入并提供 TXT 错误报告下载
+2. 2 行合法角色也不写入角色列表
+3. 角色列表、权限配置和分配用户均不产生部分导入脏数据</t>
         </is>
       </c>
       <c r="K32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
         </is>
       </c>
       <c r="L32" t="inlineStr" s="2">
@@ -2854,17 +2883,17 @@
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据权限类型</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据权限类型为空，导入失败</t>
+          <t xml:space="preserve">修正错误后重新导入成功</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F33" t="inlineStr" s="2">
@@ -2874,30 +2903,32 @@
       </c>
       <c r="G33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">反例</t>
+          <t xml:space="preserve">回归</t>
         </is>
       </c>
       <c r="H33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已准备符合模板的 Excel 文件，其中数据权限类型为空，其他字段均符合导入规则</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 已存在一次导入失败记录，失败原因为分配用户不存在
+3. 已将 Excel 中分配用户修正为系统存在的用户</t>
         </is>
       </c>
       <c r="I33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并上传该 Excel 文件
-2. 下载TXT错误报告并查看角色列表和数据权限</t>
+          <t xml:space="preserve">1. 在导入弹窗中重新上传修正后的 Excel 文件
+2. 查看导入结果和角色列表</t>
         </is>
       </c>
       <c r="J33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统拒绝全部导入，不新增角色且不写入数据权限
-2. TXT错误报告包含错误行号和数据权限类型必填原因</t>
+          <t xml:space="preserve">1. 页面提示对应条数数据导入成功
+2. 导入弹窗关闭
+3. 修正后的角色数据写入角色列表，原失败数据未残留错误状态</t>
         </is>
       </c>
       <c r="K33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
         </is>
       </c>
       <c r="L33" t="inlineStr" s="2">
@@ -2939,12 +2970,12 @@
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据权限</t>
+          <t xml:space="preserve">导出</t>
         </is>
       </c>
       <c r="D34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据权限为空，导入失败</t>
+          <t xml:space="preserve">未勾选角色时导出不可用</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
@@ -2964,20 +2995,21 @@
       </c>
       <c r="H34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已准备符合模板的 Excel 文件，数据权限类型为指定权限，数据权限为空，其他字段均符合导入规则</t>
+          <t xml:space="preserve">普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导出按钮权限</t>
         </is>
       </c>
       <c r="I34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并上传该 Excel 文件
-2. 下载TXT错误报告并查看角色列表和数据权限</t>
+          <t xml:space="preserve">1. 进入角色管理列表页
+2. 不勾选任何角色
+3. 查看导出按钮或点击导出入口</t>
         </is>
       </c>
       <c r="J34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统拒绝全部导入，不新增角色且不写入数据权限
-2. TXT错误报告包含错误行号和指定权限下数据权限必填原因</t>
+          <t xml:space="preserve">1. 导出按钮置灰不可点击，或点击后提示请至少选择一条记录
+2. 浏览器不下载导出文件
+3. 不新增导出审计记录</t>
         </is>
       </c>
       <c r="K34" t="inlineStr" s="2">
@@ -2987,7 +3019,7 @@
       </c>
       <c r="L34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M34" t="inlineStr" s="2">
@@ -3029,12 +3061,12 @@
       </c>
       <c r="D35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据权限格式不正确，导入失败</t>
+          <t xml:space="preserve">勾选单个角色导出成功</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F35" t="inlineStr" s="2">
@@ -3044,25 +3076,27 @@
       </c>
       <c r="G35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">反例</t>
+          <t xml:space="preserve">正例</t>
         </is>
       </c>
       <c r="H35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已准备符合模板的 Excel 文件，数据权限类型为指定权限，数据权限未按产品名称(产品编号)格式填写，其他字段均符合导入规则</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导出按钮权限
+2. 系统已存在角色 RM_EXPORT_001，包含菜单权限、按钮权限、分配用户和数据权限</t>
         </is>
       </c>
       <c r="I35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并上传该 Excel 文件
-2. 下载TXT错误报告并查看角色列表和数据权限</t>
+          <t xml:space="preserve">1. 进入角色管理列表页
+2. 勾选角色 RM_EXPORT_001
+3. 点击导出按钮并打开下载的 Excel 文件</t>
         </is>
       </c>
       <c r="J35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统拒绝全部导入，不新增角色且不写入数据权限
-2. TXT错误报告包含错误行号和数据权限格式应为产品名称(产品编号)的原因</t>
+          <t xml:space="preserve">1. 浏览器自动下载 Excel 文件，无需二次确认
+2. 文件名格式为角色导出_1项_YYYYMMDDHHmmss.xlsx
+3. Excel 中包含 RM_EXPORT_001 的角色基础信息和权限配置</t>
         </is>
       </c>
       <c r="K35" t="inlineStr" s="2">
@@ -3114,12 +3148,12 @@
       </c>
       <c r="D36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">产品编号或产品名称不存在，导入失败</t>
+          <t xml:space="preserve">勾选多个角色导出成功</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F36" t="inlineStr" s="2">
@@ -3129,26 +3163,27 @@
       </c>
       <c r="G36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">反例</t>
+          <t xml:space="preserve">正例</t>
         </is>
       </c>
       <c r="H36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已准备符合模板的 Excel 文件，数据权限类型为指定权限，数据权限填写不存在的产品名称或产品编号
-3. 文件中其余字段均符合导入规则</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导出按钮权限
+2. 系统已存在 3 条可导出的角色记录</t>
         </is>
       </c>
       <c r="I36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并上传该 Excel 文件
-2. 下载TXT错误报告并查看角色列表和数据权限</t>
+          <t xml:space="preserve">1. 进入角色管理列表页
+2. 勾选 3 条角色记录
+3. 点击导出按钮并打开下载的 Excel 文件</t>
         </is>
       </c>
       <c r="J36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统拒绝全部导入，不新增角色且不写入数据权限
-2. TXT错误报告包含错误行号和产品编号或产品名称不存在原因</t>
+          <t xml:space="preserve">1. 浏览器自动下载 Excel 文件
+2. 文件名格式为角色导出_3项_YYYYMMDDHHmmss.xlsx
+3. Excel 中导出 3 条角色数据，导出数量与勾选数量一致</t>
         </is>
       </c>
       <c r="K36" t="inlineStr" s="2">
@@ -3195,17 +3230,17 @@
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">多字段校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">字段多错误，导入失败</t>
+          <t xml:space="preserve">导出字段格式与模板一致</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F37" t="inlineStr" s="2">
@@ -3215,26 +3250,28 @@
       </c>
       <c r="G37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">反例</t>
+          <t xml:space="preserve">回归</t>
         </is>
       </c>
       <c r="H37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已准备符合模板的 Excel 文件，其中同一行缺少角色名称、状态为空、角色编号含空格、数据权限填写不存在的产品名称或产品编号</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导出按钮权限
+2. 系统已存在角色 RM_EXPORT_002，配置了多个菜单权限、按钮权限、分配用户和指定产品数据权限</t>
         </is>
       </c>
       <c r="I37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并上传该 Excel 文件
-2. 下载TXT错误报告并查看该行错误原因</t>
+          <t xml:space="preserve">1. 勾选角色 RM_EXPORT_002 并点击导出
+2. 打开导出的 Excel 文件
+3. 查看菜单权限、按钮权限、分配用户和数据权限字段</t>
         </is>
       </c>
       <c r="J37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统拒绝全部导入并提供TXT错误报告下载
-2. 同一行多个错误原因使用分号分隔
-3. TXT错误报告格式包含行号和错误原因</t>
+          <t xml:space="preserve">1. 导出格式与导入模版一致
+2. 菜单权限按层级路径输出，多个菜单用顿号分隔
+3. 按钮权限按菜单路径:按钮名称输出，同一菜单下多个按钮用逗号分隔，多个菜单之间用顿号分隔
+4. 分配用户和数据权限按姓名(用户账号)、产品名称(产品编号)格式输出，多个值用顿号分隔</t>
         </is>
       </c>
       <c r="K37" t="inlineStr" s="2">
@@ -3244,7 +3281,7 @@
       </c>
       <c r="L37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M37" t="inlineStr" s="2">
@@ -3276,22 +3313,22 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">稳定性</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入中重复提交，不重复写入</t>
+          <t xml:space="preserve">导出后修改再导入成功</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F38" t="inlineStr" s="2">
@@ -3306,29 +3343,29 @@
       </c>
       <c r="H38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A，拥有角色管理导入按钮权限
-2. 已准备 2000 行符合角色管理模板的 Excel 文件，且格式符合要求
-3. 已通过网络限速或测试桩使导入校验过程持续 5 秒以上</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单、导入按钮和导出按钮权限
+2. 系统已存在可导出的角色 RM_EXPORT_003
+3. 已将导出文件中的角色编码修改为系统不存在的 RM_REIMPORT_003，其他字段保持合法</t>
         </is>
       </c>
       <c r="I38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
-2. 上传大数据量 Excel 文件
-3. 校验进度展示期间连续点击上传区域或重复提交导入
-4. 等待导入完成后查看角色列表和分配用户关系</t>
+          <t xml:space="preserve">1. 勾选角色 RM_EXPORT_003 并导出 Excel 文件
+2. 修改导出文件中的角色编码为 RM_REIMPORT_003
+3. 打开导入弹窗并上传修改后的 Excel 文件
+4. 查看角色列表和新角色配置</t>
         </is>
       </c>
       <c r="J38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 导入过程中实时展示进度，上传或提交入口不可重复触发
-2. 系统只执行一次导入任务，不产生重复角色、重复用户分配或重复权限记录
-3. 最终成功条数与 Excel 有效数据行数一致</t>
+          <t xml:space="preserve">1. 系统导入成功并新增 RM_REIMPORT_003 对应角色
+2. 新角色的菜单权限、按钮权限、分配用户和数据权限与修改后的 Excel 内容一致
+3. 原角色 RM_EXPORT_003 不被覆盖或删除</t>
         </is>
       </c>
       <c r="K38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、coverage_dimension_rules.md-兼容性与稳定性</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L38" t="inlineStr" s="2">
@@ -3365,22 +3402,22 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">权限控制</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">导入权限</t>
-        </is>
-      </c>
       <c r="D39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">无导入权限，按钮隐藏</t>
+          <t xml:space="preserve">无导入权限时入口不可见</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F39" t="inlineStr" s="2">
@@ -3395,19 +3432,21 @@
       </c>
       <c r="H39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单权限但无导入按钮权限</t>
+          <t xml:space="preserve">普通用户登录业务站点 A，所属启用角色拥有角色管理菜单权限但没有角色管理导入按钮权限</t>
         </is>
       </c>
       <c r="I39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页
-2. 查看列表上方操作按钮</t>
+          <t xml:space="preserve">1. 进入配置管理下的角色管理列表页
+2. 查看列表上方操作按钮
+3. 通过导入接口直接上传 Excel 文件</t>
         </is>
       </c>
       <c r="J39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 页面不显示导入按钮
-2. 用户仍可按菜单权限查看角色列表</t>
+          <t xml:space="preserve">1. 页面不展示导入按钮
+2. 接口直接触发导入被拦截
+3. 角色列表不新增数据，且不泄露导入处理结果</t>
         </is>
       </c>
       <c r="K39" t="inlineStr" s="2">
@@ -3454,17 +3493,17 @@
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导出权限</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">无导出权限，按钮隐藏</t>
+          <t xml:space="preserve">无导出权限时入口不可见</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="F40" t="inlineStr" s="2">
@@ -3479,20 +3518,21 @@
       </c>
       <c r="H40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单权限但无导出按钮权限
-2. 角色列表存在可导出的数据</t>
+          <t xml:space="preserve">普通用户登录业务站点 A，所属启用角色拥有角色管理菜单权限但没有角色管理导出按钮权限</t>
         </is>
       </c>
       <c r="I40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 进入角色管理列表页
-2. 查看列表上方操作按钮</t>
+          <t xml:space="preserve">1. 进入配置管理下的角色管理列表页
+2. 勾选一条角色记录
+3. 查看列表上方操作按钮并通过导出接口直接请求导出</t>
         </is>
       </c>
       <c r="J40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 页面不显示导出按钮
-2. 用户仍可按菜单权限查看角色列表</t>
+          <t xml:space="preserve">1. 页面不展示导出按钮
+2. 接口直接触发导出被拦截
+3. 浏览器不下载角色数据文件</t>
         </is>
       </c>
       <c r="K40" t="inlineStr" s="2">
@@ -3502,7 +3542,7 @@
       </c>
       <c r="L40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M40" t="inlineStr" s="2">
@@ -3529,22 +3569,22 @@
     <row r="41" ht="64" customHeight="1">
       <c r="A41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">审计追踪</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">角色管理</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">接口越权</t>
+          <t xml:space="preserve">导入审计</t>
         </is>
       </c>
       <c r="D41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">越权调用导入导出接口，被拦截</t>
+          <t xml:space="preserve">导入成功记录审计日志</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -3559,32 +3599,32 @@
       </c>
       <c r="G41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">权限</t>
+          <t xml:space="preserve">回归</t>
         </is>
       </c>
       <c r="H41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单权限但无导入和导出按钮权限
-2. 已获取导入和导出请求参数用于模拟直接调用</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，拥有角色管理导入按钮权限和审计追踪菜单权限
+2. 已成功导入 3 条角色数据</t>
         </is>
       </c>
       <c r="I41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 使用无导入导出权限账号进入角色管理列表页
-2. 直接调用角色导入和导出接口
-3. 查看页面提示、下载行为和角色列表数据</t>
+          <t xml:space="preserve">1. 进入业务站点审计追踪模块
+2. 按所属模块角色管理和操作类型导入筛选
+3. 查看最新一条导入审计记录</t>
         </is>
       </c>
       <c r="J41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统拒绝导入和导出请求并返回无权限提示
-2. 导入请求不写入角色、用户分配或权限配置，导出请求不生成 Excel 文件
-3. 审计追踪不新增成功导入或成功导出记录，可记录失败原因用于排查</t>
+          <t xml:space="preserve">1. 审计追踪列表新增导入记录并显示在第一行
+2. 记录中操作人为当前用户姓名；操作时间显示格式为 yyyy-mm-dd hh:mm:ss；所属模块为角色管理；操作类型为导入
+3. 受影响对象或内容详情显示导入数量为 3</t>
         </is>
       </c>
       <c r="K41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：user_roles.md、coverage_dimension_rules.md-权限与站点隔离</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L41" t="inlineStr" s="2">
@@ -3626,12 +3666,12 @@
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">会话控制</t>
+          <t xml:space="preserve">导出审计</t>
         </is>
       </c>
       <c r="D42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">登录态过期，导入导出被拦截</t>
+          <t xml:space="preserve">导出成功记录审计日志</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -3646,33 +3686,32 @@
       </c>
       <c r="G42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">权限</t>
+          <t xml:space="preserve">回归</t>
         </is>
       </c>
       <c r="H42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 普通用户已登录业务站点 A 并拥有角色管理导入和导出按钮权限
-2. 当前登录态已过期或服务端会话已失效
-3. 角色列表存在可导出的数据，已准备符合模板的导入文件</t>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，拥有角色管理导出按钮权限和审计追踪菜单权限
+2. 已勾选 2 条角色并成功导出</t>
         </is>
       </c>
       <c r="I42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 在登录态过期后上传角色 Excel 文件
-2. 在登录态过期后点击导出按钮
-3. 查看页面跳转、提示和下载行为</t>
+          <t xml:space="preserve">1. 进入业务站点审计追踪模块
+2. 按所属模块角色管理和操作类型导出筛选
+3. 查看最新一条导出审计记录</t>
         </is>
       </c>
       <c r="J42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. 系统拦截导入和导出操作，提示登录已失效或跳转登录页
-2. 不导入角色数据，不下载角色 Excel 文件
-3. 重新登录后需按当前权限重新进入角色管理页面</t>
+          <t xml:space="preserve">1. 审计追踪列表新增导出记录并显示在第一行
+2. 记录中操作人为当前用户姓名；操作时间显示格式为 yyyy-mm-dd hh:mm:ss；所属模块为角色管理；操作类型为导出
+3. 受影响对象或内容详情显示导出数量为 2</t>
         </is>
       </c>
       <c r="K42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：user_roles.md、coverage_dimension_rules.md-权限与站点隔离</t>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
         </is>
       </c>
       <c r="L42" t="inlineStr" s="2">
@@ -3701,1399 +3740,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="64" customHeight="1">
-      <c r="A43" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">审计追踪</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">导入审计</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">导入审计详情，展示完整</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">P0</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">回归</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A，拥有角色管理导入按钮权限和审计追踪查看权限
-2. 已成功导入 3 条角色数据</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 进入业务站点审计追踪模块
-2. 按操作模块角色管理和操作类型导入筛选
-3. 点击最新导入记录的受影响对象查看详情</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 审计追踪详情基本信息展示操作人、操作时间、操作模块和操作类型
-2. 内容详情展示导入文件名、导入数量和导入数据列表
-3. 每条导入数据包含角色名称、角色编号、状态、菜单权限、按钮权限、分配用户、数据权限类型、数据权限</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd、coverage_dimension_rules.md-合规追溯</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">一般</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="64" customHeight="1">
-      <c r="A44" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">导出审计</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">导出审计详情，展示完整</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">P0</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">回归</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A，拥有角色管理导出按钮权限和审计追踪查看权限
-2. 已勾选 2 条角色并成功导出</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 进入业务站点审计追踪模块
-2. 按操作模块角色管理和操作类型导出筛选
-3. 点击最新导出记录的受影响对象查看详情</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 审计追踪详情基本信息展示操作人、操作时间、操作模块和操作类型
-2. 内容详情展示导出数量、导出环境和导出数据列表
-3. 导出数据列表包含角色名称、角色编号、状态、菜单权限、按钮权限、分配用户、数据权限类型、数据权限</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd、coverage_dimension_rules.md-合规追溯</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">一般</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="64" customHeight="1">
-      <c r="A45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">跨环境迁移</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">导出再导入</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">跨环境导出再导入，权限一致</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">P0</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">回归</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. A 环境和 B 环境均已存在相同菜单、按钮、用户账号和产品基础数据
-2. A 环境存在角色 R，包含菜单权限、按钮权限、分配用户、数据权限类型和数据权限
-3. 测试用户拥有 A 环境导出权限和 B 环境导入权限</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 在 A 环境角色管理列表勾选角色 R 并导出 Excel
-2. 在 B 环境导入该 Excel 文件
-3. 验证 B 环境角色详情和被分配用户权限</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. B 环境导入成功
-2. 角色 R 的菜单权限、按钮权限、分配用户、数据权限类型、数据权限与 A 环境导出内容一致
-3. 被分配用户在 B 环境的菜单、按钮和产品数据范围按导入配置生效</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd、difficulty_level_rules.md</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">困难</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="64" customHeight="1">
-      <c r="A46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">导入</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">模板下载</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">角色导入模板，下载成功</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">正例</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
-2. 点击下载模版
-3. 打开下载的 Excel 模板文件</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 浏览器成功下载角色管理模板
-2. 下载文件名称为角色管理模板.xlsx
-3. 模板包含预填表头行、空数据行和表头批注
-4. 表头包含角色名称、角色编号、状态、菜单权限、按钮权限、分配用户、数据权限类型、数据权限</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">一般</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="64" customHeight="1">
-      <c r="A47" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">模板基础字段说明，查询完整</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">正例</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已下载角色管理模板</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 打开角色管理模板
-2. 鼠标悬停角色名称表头查看批注
-3. 鼠标悬停角色编号表头查看批注
-4. 鼠标悬停状态表头查看批注</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 角色名称批注显示：必填，最大支持100个字符
-2. 角色编号批注显示：必填，唯一标识，支持大小写字母、数字、下划线，最大长度50个字符
-3. 状态批注显示：必填，选项为正常、停用</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">一般</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="64" customHeight="1">
-      <c r="A48" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">模板权限字段说明，查询完整</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">正例</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已下载角色管理模板</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 打开角色管理模板
-2. 鼠标悬停菜单权限表头查看批注
-3. 鼠标悬停按钮权限表头查看批注</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 菜单权限批注显示：必填，按菜单层级路径填写，父菜单与子菜单用“/”分隔，多个菜单用顿号分隔，并包含菜单路径示例；勾选父级菜单表示同时拥有其下所有子菜单权限
-2. 按钮权限批注显示：选填，填写时按“所属菜单路径:按钮名称1，按钮名称2”格式填写，同一菜单下多个按钮用逗号隔开，多个菜单之间用顿号分隔，并包含按钮权限示例；按钮名称需与系统内按钮名称一致</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">一般</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="64" customHeight="1">
-      <c r="A49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">模板用户与数据权限字段说明，查询完整</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">正例</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已下载角色管理模板</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 打开角色管理模板
-2. 鼠标悬停分配用户表头查看批注
-3. 鼠标悬停数据权限类型表头查看批注
-4. 鼠标悬停数据权限表头查看批注</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 分配用户批注显示：选填，格式为姓名(用户账号)，多个用户用顿号分隔，并包含用户示例；为空表示该角色暂无分配用户
-2. 数据权限类型批注显示：必填，选项为全部权限、指定权限
-3. 数据权限批注显示：选填；数据权限类型为指定权限时必填，格式为产品名称(产品编号)，多个产品用顿号分隔，并包含产品示例；数据权限类型为全部权限时可任意填写或留空，导入后按全部权限保存</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">一般</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="64" customHeight="1">
-      <c r="A50" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">状态字段支持下拉选择，选项正确</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">正例</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已下载角色管理模板</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 打开角色管理模板
-2. 定位状态列的可编辑数据行
-3. 点击单元格下拉并查看可选项
-4. 尝试选择各下拉项并保存模板</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 状态列支持通过下拉选择录入
-2. 下拉选项仅包含正常、停用
-3. 选择正常或停用后模板可正常保存</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">一般</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="64" customHeight="1">
-      <c r="A51" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">数据权限类型支持下拉选择，选项正确</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">正例</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已下载角色管理模板</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 打开角色管理模板
-2. 定位数据权限类型列的可编辑数据行
-3. 点击单元格下拉并查看可选项
-4. 尝试选择各下拉项并保存模板</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 数据权限类型列支持通过下拉选择录入
-2. 下拉选项仅包含全部权限、指定权限
-3. 选择全部权限或指定权限后模板可正常保存</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">一般</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="64" customHeight="1">
-      <c r="A52" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">导入弹窗</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">导入弹窗，展示完整</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">UI</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并点击导入按钮
-2. 查看导入弹窗内容</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 导入弹窗展示下载模版区域和上传文件区域
-2. 上传控件默认筛选 .xlsx 和 .xls 文件类型</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">一般</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="64" customHeight="1">
-      <c r="A53" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">失败报告</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">TXT错误报告，下载成功</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">反例</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导入按钮权限
-2. 已上传包含业务校验错误的角色 Excel 文件，系统已校验失败</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 在导入失败弹窗中点击TXT错误报告下载
-2. 打开下载的 TXT 文件
-3. 查看TXT错误报告内容</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 浏览器成功下载TXT错误报告
-2. TXT错误报告每条记录包含行号和错误原因
-3. 导入弹窗保持开启，便于用户修正后重新上传</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">一般</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="64" customHeight="1">
-      <c r="A54" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">导出</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">导出成功</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">勾选角色，导出成功</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">正例</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导出按钮权限
-2. 角色列表存在 2 条字段完整的可导出角色</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 进入角色管理列表页并勾选 2 条角色
-2. 点击导出并打开下载的 Excel 文件</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 浏览器自动下载 Excel 文件，无需二次确认
-2. 导出文件名符合角色导出_2项_YYYYMMDDHHmmss.xlsx 格式
-3. Excel 内容包含角色名称、角色编号、状态、菜单权限、按钮权限、分配用户、数据权限类型、数据权限，且数据与页面一致</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">一般</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="64" customHeight="1">
-      <c r="A55" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">导出格式</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">菜单权限和按钮权限有多个时，导出正确</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">正例</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导出按钮权限
-2. 角色 R 拥有计划管理/年度计划设置、配置管理/产品管理等多个菜单权限，以及新增、删除、导入等按钮权限</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 进入角色管理列表页
-2. 勾选角色 R 并点击导出
-3. 打开下载的 Excel 文件查看菜单权限和按钮权限字段</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 菜单权限按层级路径输出，多个菜单以顿号分隔，例如计划管理/年度计划设置、配置管理/产品管理
-2. 按钮权限按“菜单路径:按钮名称1，按钮名称2”输出，同一菜单下多个按钮用逗号分隔，多个菜单之间用顿号分隔，例如计划管理/年度计划设置:新增，删除、配置管理/产品管理:导入</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">一般</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="64" customHeight="1">
-      <c r="A56" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">导出文件修改后，再次导入成功</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">回归</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理导入和导出按钮权限
-2. 已成功导出角色 Excel 文件，并修改角色编号为新的唯一编码</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 返回角色管理列表页并上传修改后的导出 Excel 文件
-2. 查看导入提示、角色列表和新角色配置详情</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 修改后的角色数据导入成功
-2. 新角色的菜单权限、按钮权限、分配用户、数据权限类型、数据权限与 Excel 内容一致
-3. 导出文件字段格式可被导入流程识别</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">一般</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="64" customHeight="1">
-      <c r="A57" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">导出异常</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">未勾选角色，导出被拦截</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">反例</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导出按钮权限
-2. 角色列表存在可导出数据，但当前未勾选任何角色</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 进入角色管理列表页
-2. 不勾选任何角色
-3. 查看导出按钮状态并尝试点击导出</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 导出按钮置灰或点击后提示请至少选择一条记录
-2. 不触发浏览器下载 Excel 文件
-3. 角色列表选择状态保持不变</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">一般</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="64" customHeight="1">
-      <c r="A58" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">导出过程中断，提示重试</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">反例</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A 并拥有角色管理导出按钮权限
-2. 角色列表已勾选 5 条角色
-3. 已通过网络限速或测试桩模拟导出过程中网络中断</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 进入角色管理列表页
-2. 勾选 5 条角色并点击导出
-3. 在下载过程中触发网络中断
-4. 查看页面提示和浏览器下载结果</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 系统提示导出失败或允许用户重试
-2. 浏览器不保留损坏的完整交付文件
-3. 角色列表勾选状态不导致业务数据变化，审计追踪不新增成功导出记录</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：coverage_dimension_rules.md-兼容性与稳定性、negative_flow_template.md</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">一般</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P58"/>
+  <autoFilter ref="A1:P42"/>
 </worksheet>
 </file>
--- a/.claude/skills/testcase-generator/outputs/excel_exports/business_site/role_manage_import_export_testcases.xlsx
+++ b/.claude/skills/testcase-generator/outputs/excel_exports/business_site/role_manage_import_export_testcases.xlsx
@@ -77,7 +77,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P46"/>
+  <dimension ref="A1:P51"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -192,542 +192,630 @@
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">导入成功</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">导入后角色权限生效</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">回归</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 系统已存在用户李四(lisi02)和产品阿托伐他汀钙片(TAB-005)
+3. 待上传 Excel 包含角色 RM_IMPORT_006，菜单权限包含计划管理/年度计划设置，按钮权限包含计划管理/年度计划设置:新增，分配用户为李四(lisi02)，数据权限为阿托伐他汀钙片(TAB-005)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 导入角色 RM_IMPORT_006
+2. 使用李四账号重新登录业务站点 A
+3. 进入年度计划设置列表并点击新增</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 李四可见年度计划设置菜单和新增按钮
+2. 新增计划弹窗的所属产品下拉仅展示阿托伐他汀钙片
+3. 不在该角色权限内的菜单或按钮不展示</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：prd、user_roles.md、priority_rules.md-P0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">困难</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="64" customHeight="1">
+      <c r="A3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">导入模板</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr" s="2">
+      <c r="D3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">下载角色导入模板成功</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr" s="2">
+      <c r="E3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr" s="2">
+      <c r="F3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">正例</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr" s="2">
+      <c r="H3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr" s="2">
+      <c r="I3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入配置管理下的角色管理列表页
 2. 点击列表上方的导入按钮
 3. 在导入弹窗中点击下载模版</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr" s="2">
+      <c r="J3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 浏览器下载 Excel 模版文件
 2. 模版名称为角色管理模板
 3. 导入弹窗保持可操作，可继续上传 Excel 文件</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr" s="2">
+      <c r="K3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr" s="2">
+      <c r="L3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">简单</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="64" customHeight="1">
-      <c r="A3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr" s="2">
+      <c r="M3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="64" customHeight="1">
+      <c r="A4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">模板表头和下拉选项显示正确</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr" s="2">
+      <c r="E4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr" s="2">
+      <c r="F4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">UI</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr" s="2">
+      <c r="H4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr" s="2">
+      <c r="I4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 下载角色管理导入模版
 2. 打开 Excel 模版并查看表头和下拉选项</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr" s="2">
+      <c r="J4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 模版包含角色名称、角色编码、状态、菜单权限、按钮权限、分配用户、数据权限类型、数据权限表头
 2. 状态下拉选项包含正常、停用
 3. 数据权限类型下拉选项包含全部权限、指定权限</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr" s="2">
+      <c r="K4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">简单</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="64" customHeight="1">
-      <c r="A4" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr" s="2">
+      <c r="M4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="64" customHeight="1">
+      <c r="A5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">基础信息字段批注显示正确</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr" s="2">
+      <c r="E5" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr" s="2">
+      <c r="F5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">UI</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr" s="2">
+      <c r="H5" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr" s="2">
+      <c r="I5" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 下载角色管理导入模版
 2. 打开 Excel 模版并悬停查看角色名称和角色编码表头批注</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr" s="2">
+      <c r="J5" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 角色名称批注显示：必填，最大支持100个字符
 2. 角色编码批注显示：必填，唯一标识，支持大写字母、数字、下划线，最大长度50个字符</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr" s="2">
+      <c r="K5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">简单</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="64" customHeight="1">
-      <c r="A5" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr" s="2">
+      <c r="M5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="64" customHeight="1">
+      <c r="A6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">权限字段批注显示正确</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr" s="2">
+      <c r="E6" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr" s="2">
+      <c r="F6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">UI</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr" s="2">
+      <c r="H6" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr" s="2">
+      <c r="I6" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 下载角色管理导入模版
 2. 打开 Excel 模版并悬停查看菜单权限和按钮权限表头批注</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr" s="2">
+      <c r="J6" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 菜单权限批注显示：必填，菜单层级路径，父菜单与子菜单用“/”分隔，多个菜单用顿号分隔
 2. 按钮权限批注显示：必填，按钮权限格式为“所属菜单路径:按钮名称1，按钮名称2”，同一菜单下多个按钮用逗号隔开，多个菜单之间用顿号分隔</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr" s="2">
+      <c r="K6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">简单</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="64" customHeight="1">
-      <c r="A6" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr" s="2">
+      <c r="M6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="64" customHeight="1">
+      <c r="A7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">用户和数据权限批注显示正确</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr" s="2">
+      <c r="E7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr" s="2">
+      <c r="F7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">UI</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr" s="2">
+      <c r="H7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr" s="2">
+      <c r="I7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 下载角色管理导入模版
 2. 打开 Excel 模版并悬停查看分配用户、数据权限类型和数据权限表头批注</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr" s="2">
+      <c r="J7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 分配用户批注显示：选填，格式为姓名(用户账号)，多个用户用顿号分隔，若为空则表示该角色暂无分配用户
 2. 数据权限类型批注显示：必填，选项：全部权限、指定权限
 3. 数据权限批注显示：选填，当数据权限类型为“指定权限”时必填，格式为产品名称(产品编号)，多个产品用顿号分隔，当数据权限类型为“全部权限”时填写“全部”或留空即可</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr" s="2">
+      <c r="K7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">简单</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="64" customHeight="1">
-      <c r="A7" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr" s="2">
+      <c r="M7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="64" customHeight="1">
+      <c r="A8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">导入成功</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr" s="2">
+      <c r="D8" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">只填必填字段导入成功</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr" s="2">
+      <c r="E8" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr" s="2">
+      <c r="F8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">正例</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr" s="2">
+      <c r="H8" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
 2. 系统不存在角色编码 RM_IMPORT_001
 3. 待上传 Excel 为 .xlsx 格式，填写角色名称、角色编码、状态、菜单权限、按钮权限和数据权限类型，分配用户和数据权限为空</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr" s="2">
+      <c r="I8" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
 2. 上传待上传 Excel 文件
 3. 查看导入结果和角色列表</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr" s="2">
+      <c r="J8" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 页面提示 1 条数据导入成功
 2. 导入弹窗关闭，角色列表新增 RM_IMPORT_001 对应角色
 3. 新增角色的状态、菜单权限和按钮权限与 Excel 内容一致</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr" s="2">
+      <c r="K8" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr" s="2">
+      <c r="L8" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">一般</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="64" customHeight="1">
-      <c r="A8" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr" s="2">
+      <c r="M8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="64" customHeight="1">
+      <c r="A9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">指定权限和用户导入成功</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr" s="2">
+      <c r="E9" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr" s="2">
+      <c r="F9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">正例</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr" s="2">
+      <c r="H9" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
 2. 系统已存在用户张三(zhangsan01)和产品维生素A片(VIT-001)
@@ -735,380 +823,292 @@
 4. 待上传 Excel 中数据权限类型为指定权限，数据权限填写维生素A片(VIT-001)，分配用户填写张三(zhangsan01)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr" s="2">
+      <c r="I9" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
 2. 上传待上传 Excel 文件
 3. 查看角色详情、产品数据权限和分配用户详情</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr" s="2">
+      <c r="J9" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 页面提示 1 条数据导入成功
 2. 角色列表新增 RM_IMPORT_002 对应角色
 3. 产品数据权限详情显示维生素A片和 VIT-001，分配用户详情显示张三和 zhangsan01</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr" s="2">
+      <c r="K9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：prd、user_roles.md</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">一般</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="64" customHeight="1">
-      <c r="A9" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr" s="2">
+      <c r="M9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="64" customHeight="1">
+      <c r="A10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">多行角色整体导入成功</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr" s="2">
+      <c r="E10" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr" s="2">
+      <c r="F10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">正例</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr" s="2">
+      <c r="H10" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
 2. 系统不存在角色编码 RM_IMPORT_003、RM_IMPORT_004、RM_IMPORT_005
 3. 待上传 Excel 包含 3 行合法角色数据</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr" s="2">
+      <c r="I10" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
 2. 上传包含 3 行合法数据的 Excel 文件
 3. 查看导入结果和角色列表</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr" s="2">
+      <c r="J10" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 页面提示 3 条数据导入成功
 2. 角色列表新增 3 条对应角色记录
 3. 每条角色的基础信息、状态、菜单权限、按钮权限、分配用户和数据权限与 Excel 内容一致</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr" s="2">
+      <c r="K10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">一般</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="64" customHeight="1">
-      <c r="A10" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr" s="2">
+      <c r="M10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="64" customHeight="1">
+      <c r="A11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">角色名称100字符导入成功</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr" s="2">
+      <c r="E11" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr" s="2">
+      <c r="F11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">边界</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr" s="2">
+      <c r="H11" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
 2. 系统不存在角色编码 RM_IMPORT_007
 3. 待上传 Excel 中角色名称为 100 个字符，其他必填字段合法</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr" s="2">
+      <c r="I11" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
 2. 上传角色名称为 100 个字符的 Excel 文件
 3. 查看导入结果和角色列表</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr" s="2">
+      <c r="J11" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 页面提示 1 条数据导入成功
 2. 角色列表新增 RM_IMPORT_007 对应角色
 3. 新增角色的角色名称完整保存并展示为 100 个字符</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr" s="2">
+      <c r="K11" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr" s="2">
+      <c r="L11" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">一般</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="64" customHeight="1">
-      <c r="A11" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr" s="2">
+      <c r="M11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="64" customHeight="1">
+      <c r="A12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">角色编码50字符导入成功</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr" s="2">
+      <c r="E12" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr" s="2">
+      <c r="F12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">边界</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr" s="2">
+      <c r="H12" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
 2. 系统不存在待导入的 50 字符角色编码
 3. 待上传 Excel 中角色编码为 50 个字符且只包含大写字母、数字、下划线，其他必填字段合法</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr" s="2">
+      <c r="I12" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
 2. 上传角色编码为 50 个字符的 Excel 文件
 3. 查看导入结果和角色列表</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr" s="2">
+      <c r="J12" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 页面提示 1 条数据导入成功
 2. 角色列表新增对应角色记录
 3. 新增角色的角色编码完整保存并展示为 50 个字符</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr" s="2">
+      <c r="K12" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr" s="2">
+      <c r="L12" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">一般</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="64" customHeight="1">
-      <c r="A12" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">导入后角色权限生效</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">P0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">回归</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
-2. 系统已存在用户李四(lisi02)和产品阿托伐他汀钙片(TAB-005)
-3. 待上传 Excel 包含角色 RM_IMPORT_006，菜单权限包含计划管理/年度计划设置，按钮权限包含计划管理/年度计划设置:新增，分配用户为李四(lisi02)，数据权限为阿托伐他汀钙片(TAB-005)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 导入角色 RM_IMPORT_006
-2. 使用李四账号重新登录业务站点 A
-3. 进入年度计划设置列表并点击新增</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 李四可见年度计划设置菜单和新增按钮
-2. 新增计划弹窗的所属产品下拉仅展示阿托伐他汀钙片
-3. 不在该角色权限内的菜单或按钮不展示</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd、user_roles.md</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M12" t="inlineStr" s="2">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">导入失败校验</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">导入失败校验</t>
+          <t xml:space="preserve">文件类型</t>
         </is>
       </c>
       <c r="D13" t="inlineStr" s="2">
@@ -1183,13 +1183,13 @@
       <c r="J13" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 系统阻止上传或导入
-2. 页面提示请上传 Excel 文件（.xlsx或.xls格式）
+2. 页面提示请上传Excel文件（.xlsx或.xls格式）
 3. 角色列表不新增数据</t>
         </is>
       </c>
       <c r="K13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
         </is>
       </c>
       <c r="L13" t="inlineStr" s="2">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">文件大小</t>
         </is>
       </c>
       <c r="D14" t="inlineStr" s="2">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
         </is>
       </c>
       <c r="L14" t="inlineStr" s="2">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">空文件</t>
         </is>
       </c>
       <c r="D15" t="inlineStr" s="2">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="K15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
         </is>
       </c>
       <c r="L15" t="inlineStr" s="2">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">无有效数据</t>
         </is>
       </c>
       <c r="D16" t="inlineStr" s="2">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="K16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
         </is>
       </c>
       <c r="L16" t="inlineStr" s="2">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">表头</t>
         </is>
       </c>
       <c r="D17" t="inlineStr" s="2">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="K17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
         </is>
       </c>
       <c r="L17" t="inlineStr" s="2">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
         </is>
       </c>
       <c r="L18" t="inlineStr" s="2">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">合并单元格</t>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="2">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="K19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
         </is>
       </c>
       <c r="L19" t="inlineStr" s="2">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">文件解析</t>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="2">
@@ -1785,13 +1785,13 @@
       <c r="J20" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 系统终止导入
-2. 页面提示 Excel解析失败，请检查格式等信息。
+2. 页面提示Excel解析失败，请检查格式等信息。
 3. 角色列表不新增数据</t>
         </is>
       </c>
       <c r="K20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
         </is>
       </c>
       <c r="L20" t="inlineStr" s="2">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="K21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd、import_coverage_rules.md</t>
         </is>
       </c>
       <c r="L21" t="inlineStr" s="2">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">角色名称</t>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="2">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">角色编码</t>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="2">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">菜单权限</t>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="2">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">按钮权限</t>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="2">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">分配用户</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="2">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">数据权限类型</t>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="2">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">数据权限</t>
         </is>
       </c>
       <c r="D33" t="inlineStr" s="2">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">角色管理</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="D38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">未勾选角色时导出不可用</t>
+          <t xml:space="preserve">导出字段格式与模板一致</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="F38" t="inlineStr" s="2">
@@ -3332,365 +3332,105 @@
       </c>
       <c r="G38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">反例</t>
+          <t xml:space="preserve">回归</t>
         </is>
       </c>
       <c r="H38" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导出按钮权限</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 进入角色管理列表页
-2. 不勾选任何角色
-3. 查看导出按钮或点击导出入口</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 导出按钮置灰不可点击，或点击后提示请至少选择一条记录
-2. 浏览器不下载导出文件
-3. 不新增导出审计记录</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">简单</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="64" customHeight="1">
-      <c r="A39" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">勾选单个角色导出成功</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">正例</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导出按钮权限
-2. 系统已存在角色 RM_EXPORT_001，包含菜单权限、按钮权限、分配用户和数据权限</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 进入角色管理列表页
-2. 勾选角色 RM_EXPORT_001
-3. 点击导出按钮并打开下载的 Excel 文件</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 浏览器自动下载 Excel 文件，无需二次确认
-2. 文件名格式为角色导出_1项_YYYYMMDDHHmmss.xlsx
-3. Excel 中包含 RM_EXPORT_001 的角色基础信息和权限配置</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">一般</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="64" customHeight="1">
-      <c r="A40" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">勾选多个角色导出成功</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">正例</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导出按钮权限
-2. 系统已存在 3 条可导出的角色记录</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 进入角色管理列表页
-2. 勾选 3 条角色记录
-3. 点击导出按钮并打开下载的 Excel 文件</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 浏览器自动下载 Excel 文件
-2. 文件名格式为角色导出_3项_YYYYMMDDHHmmss.xlsx
-3. Excel 中导出 3 条角色数据，导出数量与勾选数量一致</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">一般</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="64" customHeight="1">
-      <c r="A41" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">导出字段格式与模板一致</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">P0</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">回归</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导出按钮权限
 2. 系统已存在角色 RM_EXPORT_002，配置了多个菜单权限、按钮权限、分配用户和指定产品数据权限</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr" s="2">
+      <c r="I38" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 勾选角色 RM_EXPORT_002 并点击导出
 2. 打开导出的 Excel 文件
 3. 查看菜单权限、按钮权限、分配用户和数据权限字段</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr" s="2">
+      <c r="J38" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 导出格式与导入模版一致
 2. 菜单权限按层级路径输出，多个菜单用顿号分隔
-3. 按钮权限按菜单路径:按钮名称输出，同一菜单下多个按钮用逗号分隔，多个菜单之间用顿号分隔
+3. 按钮权限按菜单路径:按钮名称输出，同一菜单下多个按钮用逗号隔开，多个菜单之间用顿号分隔
 4. 分配用户和数据权限按姓名(用户账号)、产品名称(产品编号)格式输出，多个值用顿号分隔</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr" s="2">
+      <c r="K38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：prd、priority_rules.md-P0</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">困难</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="64" customHeight="1">
-      <c r="A42" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr" s="2">
+      <c r="M38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="64" customHeight="1">
+      <c r="A39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">导出后修改再导入成功</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr" s="2">
+      <c r="E39" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P0</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr" s="2">
+      <c r="F39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">回归</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr" s="2">
+      <c r="H39" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单、导入按钮和导出按钮权限
 2. 系统已存在可导出的角色 RM_EXPORT_003
 3. 已将导出文件中的角色编码修改为系统不存在的 RM_REIMPORT_003，其他字段保持合法</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr" s="2">
+      <c r="I39" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 勾选角色 RM_EXPORT_003 并导出 Excel 文件
 2. 修改导出文件中的角色编码为 RM_REIMPORT_003
@@ -3698,13 +3438,273 @@
 4. 查看角色列表和新角色配置</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr" s="2">
+      <c r="J39" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 系统导入成功并新增 RM_REIMPORT_003 对应角色
 2. 新角色的菜单权限、按钮权限、分配用户和数据权限与修改后的 Excel 内容一致
 3. 原角色 RM_EXPORT_003 不被覆盖或删除</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：prd、priority_rules.md-P0</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">一般</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="64" customHeight="1">
+      <c r="A40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">勾选单个角色导出成功</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">正例</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导出按钮权限
+2. 系统已存在角色 RM_EXPORT_001，包含菜单权限、按钮权限、分配用户和数据权限</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 进入角色管理列表页
+2. 勾选角色 RM_EXPORT_001
+3. 点击导出按钮并打开下载的 Excel 文件</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 浏览器自动下载 Excel 文件，无需二次确认
+2. 文件名格式为角色导出_1项_YYYYMMDDHHmmss.xlsx
+3. Excel 中包含 RM_EXPORT_001 的角色基础信息和权限配置</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：prd</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">一般</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="64" customHeight="1">
+      <c r="A41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">勾选多个角色导出成功</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">正例</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导出按钮权限
+2. 系统已存在 3 条可导出的角色记录</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 进入角色管理列表页
+2. 勾选 3 条角色记录
+3. 点击导出按钮并打开下载的 Excel 文件</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 浏览器自动下载 Excel 文件
+2. 文件名格式为角色导出_3项_YYYYMMDDHHmmss.xlsx
+3. Excel 中导出 3 条角色数据，导出数量与勾选数量一致</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：prd</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">一般</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="64" customHeight="1">
+      <c r="A42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">未勾选角色时导出不可用</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">反例</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导出按钮权限</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 进入角色管理列表页
+2. 不勾选任何角色
+3. 查看导出按钮或点击导出入口</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 导出按钮置灰不可点击，或点击后提示请至少选择一条记录
+2. 浏览器不下载导出文件
+3. 不新增导出审计记录</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">来源：prd</t>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="L42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">简单</t>
         </is>
       </c>
       <c r="M42" t="inlineStr" s="2">
@@ -3911,178 +3911,611 @@
     <row r="45" ht="64" customHeight="1">
       <c r="A45" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">无角色管理菜单权限时不可访问导入导出</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">权限</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">普通用户登录业务站点 A，所属启用角色无角色管理菜单权限</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 查看业务站点配置管理菜单
+2. 通过角色管理列表 URL 直接访问
+3. 通过导入或导出接口直接发起请求</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 页面不展示角色管理菜单入口
+2. URL 直接访问被拦截，不展示角色列表
+3. 导入和导出接口请求被拦截，不返回角色数据或导入处理结果</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：user_roles.md、coverage_dimension_rules.md</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">一般</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="64" customHeight="1">
+      <c r="A46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">站点隔离</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">跨业务站点不可导入导出角色数据</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">权限</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 普通用户已登录业务站点 B，所属启用角色拥有业务站点 B 的角色管理导入导出权限
+2. 业务站点 A 已存在角色 R_A，当前用户无业务站点 A 访问权限</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 在业务站点 B 进入角色管理列表
+2. 上传包含业务站点 A 角色编码或产品编号的导入文件
+3. 通过业务站点 A 的角色导出接口直接请求导出</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 导入时仅按业务站点 B 的用户、产品和权限数据校验，不写入业务站点 A 数据
+2. 直接请求业务站点 A 导出接口被拦截，不返回角色数据文件</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：user_roles.md、coverage_dimension_rules.md</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">一般</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="64" customHeight="1">
+      <c r="A47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">稳定性</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">重复点击导入不产生重复角色</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">回归</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导入按钮权限
+2. 待上传 Excel 包含 1 条系统不存在的角色编码 RM_IMPORT_REPEAT</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 进入角色管理列表页并打开导入弹窗
+2. 上传待上传 Excel 文件
+3. 在上传后快速重复点击导入或重复提交入口</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 系统只处理一次导入请求
+2. 角色列表仅新增 1 条 RM_IMPORT_REPEAT 对应角色
+3. 审计追踪不生成重复导入记录</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：coverage_dimension_rules.md-兼容性与稳定性</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">一般</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="64" customHeight="1">
+      <c r="A48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">重复点击导出不产生重复任务</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">回归</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，所属启用角色拥有角色管理菜单和导出按钮权限
+2. 角色管理列表存在 1 条可导出角色</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 勾选目标角色
+2. 快速重复点击导出按钮
+3. 查看浏览器下载记录和审计追踪记录</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 系统不生成重复导出任务或重复下载多个同内容文件
+2. 导出期间按钮展示禁用或加载状态
+3. 审计追踪不生成重复导出记录</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：coverage_dimension_rules.md-兼容性与稳定性</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">一般</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="64" customHeight="1">
+      <c r="A49" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">审计追踪</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr" s="2">
+      <c r="B49" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">角色管理</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr" s="2">
+      <c r="C49" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">导入审计</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr" s="2">
+      <c r="D49" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">导入成功记录审计日志</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr" s="2">
+      <c r="E49" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P0</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr" s="2">
+      <c r="F49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">回归</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr" s="2">
+      <c r="H49" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 普通用户登录业务站点 A，拥有角色管理导入按钮权限和审计追踪菜单权限
 2. 已成功导入 3 条角色数据</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr" s="2">
+      <c r="I49" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入业务站点审计追踪模块
 2. 按所属模块角色管理和操作类型导入筛选
 3. 查看最新一条导入审计记录</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr" s="2">
+      <c r="J49" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 审计追踪列表新增导入记录并显示在第一行
 2. 记录中操作人为当前用户姓名；操作时间显示格式为 yyyy-mm-dd hh:mm:ss；所属模块为角色管理；操作类型为导入
 3. 受影响对象或内容详情显示导入数量为 3</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr" s="2">
+      <c r="K49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md、priority_rules.md-P0</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">一般</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="64" customHeight="1">
-      <c r="A46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr" s="2">
+      <c r="M49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="64" customHeight="1">
+      <c r="A50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">导出审计</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr" s="2">
+      <c r="D50" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">导出成功记录审计日志</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr" s="2">
+      <c r="E50" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P0</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr" s="2">
+      <c r="F50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">回归</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr" s="2">
+      <c r="H50" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 普通用户登录业务站点 A，拥有角色管理导出按钮权限和审计追踪菜单权限
 2. 已勾选 2 条角色并成功导出</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr" s="2">
+      <c r="I50" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入业务站点审计追踪模块
 2. 按所属模块角色管理和操作类型导出筛选
 3. 查看最新一条导出审计记录</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr" s="2">
+      <c r="J50" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 审计追踪列表新增导出记录并显示在第一行
 2. 记录中操作人为当前用户姓名；操作时间显示格式为 yyyy-mm-dd hh:mm:ss；所属模块为角色管理；操作类型为导出
 3. 受影响对象或内容详情显示导出数量为 2</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr" s="2">
+      <c r="K50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：prd、audit_trail_coverage_rules.md、priority_rules.md-P0</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">一般</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr" s="2">
+      <c r="M50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="64" customHeight="1">
+      <c r="A51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">导入审计</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">导入失败不生成成功审计记录</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">反例</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 普通用户登录业务站点 A，拥有角色管理导入按钮权限和审计追踪菜单权限
+2. 待上传 Excel 存在角色编码重复错误</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 上传存在错误的 Excel 文件
+2. 下载 TXT 错误报告
+3. 进入业务站点审计追踪模块查看角色管理导入记录</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 审计追踪不新增导入成功记录
+2. 角色列表不写入错误文件中的角色数据
+3. 错误报告仍可从导入弹窗下载</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：import_coverage_rules.md、audit_trail_coverage_rules.md</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">一般</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P46"/>
+  <autoFilter ref="A1:P51"/>
 </worksheet>
 </file>